--- a/html/WTMA_SkillTest_Questions_new.xlsx
+++ b/html/WTMA_SkillTest_Questions_new.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\preejith\REC\2026\WTMA\others\skill_test\wtma_skilltest_package\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\preejith\REC\2026\WTMA\WTMA_LAB\WTMA-Lab\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECDA19CE-8C27-4ACB-A745-290DFDF93706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19276C52-0531-46C6-A70C-DC5487351D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -301,28 +301,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -626,7 +605,7 @@
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="28.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="255.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="63" customWidth="1"/>
+    <col min="4" max="4" width="204.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
@@ -1270,7 +1249,7 @@
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1309,7 +1288,7 @@
         <v>54</v>
       </c>
       <c r="C49" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="D49" t="s">
         <v>3</v>
@@ -1326,7 +1305,7 @@
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1351,10 +1330,10 @@
         <v>57</v>
       </c>
       <c r="C52" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1365,7 +1344,7 @@
         <v>58</v>
       </c>
       <c r="C53" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D53" t="s">
         <v>78</v>
@@ -1396,7 +1375,7 @@
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>4</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1480,7 +1459,7 @@
         <v>78</v>
       </c>
       <c r="D61" t="s">
-        <v>79</v>
+        <v>5</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">

--- a/html/WTMA_SkillTest_Questions_new.xlsx
+++ b/html/WTMA_SkillTest_Questions_new.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\preejith\REC\2026\WTMA\WTMA_LAB\WTMA-Lab\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19276C52-0531-46C6-A70C-DC5487351D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79FDC480-9CD7-4C9B-9EB7-726FF53D4D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1003" uniqueCount="343">
   <si>
     <t>Question1</t>
   </si>
@@ -94,9 +94,6 @@
     <t>Luei Johncena J</t>
   </si>
   <si>
-    <t>Madhan Rasamalla Venkatesalu</t>
-  </si>
-  <si>
     <t>Mageshwaran G</t>
   </si>
   <si>
@@ -208,9 +205,6 @@
     <t>M Sri Ramkanna</t>
   </si>
   <si>
-    <t>Sujitha Neelakandan Vigneshwari</t>
-  </si>
-  <si>
     <t>B Sunetra</t>
   </si>
   <si>
@@ -256,10 +250,817 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Design an html Registration page with following fields of the Registration page: First Name, Password, E-mail ID, Mobile Number, Last Name and Address. Write JavaScript to validate the fields as per the validation rules.</t>
-  </si>
-  <si>
-    <t>Design an HTML Employee Details page with fields for Employee ID, Name, and Designation. Include four salary components: Basic Pay, DA, HRA, and Allowance. When the user clicks the "Show Salary" button, calculate and display the final salary.</t>
+    <t>Aakash A</t>
+  </si>
+  <si>
+    <t>Abdul Kalam B</t>
+  </si>
+  <si>
+    <t>Abhijith K</t>
+  </si>
+  <si>
+    <t>Abhinaya R D</t>
+  </si>
+  <si>
+    <t>Abiram G</t>
+  </si>
+  <si>
+    <t>Adhilakshmi L</t>
+  </si>
+  <si>
+    <t>Adithyasundar R</t>
+  </si>
+  <si>
+    <t>Aiswariya A</t>
+  </si>
+  <si>
+    <t>Akash M</t>
+  </si>
+  <si>
+    <t>Akshaya B</t>
+  </si>
+  <si>
+    <t>Akshaya D</t>
+  </si>
+  <si>
+    <t>Akshaya P</t>
+  </si>
+  <si>
+    <t>Akshaya P A</t>
+  </si>
+  <si>
+    <t>Akshaya V S</t>
+  </si>
+  <si>
+    <t>Ambrish Kumar A</t>
+  </si>
+  <si>
+    <t>Ananthi S</t>
+  </si>
+  <si>
+    <t>Andryan Durai Jebin</t>
+  </si>
+  <si>
+    <t>Angelin Blessy J A</t>
+  </si>
+  <si>
+    <t>Angelin Shreya C</t>
+  </si>
+  <si>
+    <t>Anisha S</t>
+  </si>
+  <si>
+    <t>Anvitha A</t>
+  </si>
+  <si>
+    <t>Aravindh K</t>
+  </si>
+  <si>
+    <t>Archana D</t>
+  </si>
+  <si>
+    <t>Ashwanth S</t>
+  </si>
+  <si>
+    <t>S Attana</t>
+  </si>
+  <si>
+    <t>Balamurugan R</t>
+  </si>
+  <si>
+    <t>Bharath Kumar S</t>
+  </si>
+  <si>
+    <t>Bowmiga R</t>
+  </si>
+  <si>
+    <t>Callistus L</t>
+  </si>
+  <si>
+    <t>Chandhru L</t>
+  </si>
+  <si>
+    <t>I Daniel Jonathan</t>
+  </si>
+  <si>
+    <t>Darshan C S</t>
+  </si>
+  <si>
+    <t>Darshan S</t>
+  </si>
+  <si>
+    <t>S P Darshan</t>
+  </si>
+  <si>
+    <t>Deepak V</t>
+  </si>
+  <si>
+    <t>Deepika S</t>
+  </si>
+  <si>
+    <t>Deepika V</t>
+  </si>
+  <si>
+    <t>Deiva Lakshmee Alagu
+Arumugam</t>
+  </si>
+  <si>
+    <t>Devesh N</t>
+  </si>
+  <si>
+    <t>Devyesh C</t>
+  </si>
+  <si>
+    <t>Dhanusri Ramakrishnan
+Suresh Babu</t>
+  </si>
+  <si>
+    <t>Dharsan K</t>
+  </si>
+  <si>
+    <t>J B Dhejasvi</t>
+  </si>
+  <si>
+    <t>J Dhinesh</t>
+  </si>
+  <si>
+    <t>Dhyanesh M</t>
+  </si>
+  <si>
+    <t>Dillibabu J</t>
+  </si>
+  <si>
+    <t>Dinesh G</t>
+  </si>
+  <si>
+    <t>S Divya Darshini</t>
+  </si>
+  <si>
+    <t>Divya Lakshmi Dinesh
+Kumar</t>
+  </si>
+  <si>
+    <t>Divya Priya M</t>
+  </si>
+  <si>
+    <t>Divyadharani J</t>
+  </si>
+  <si>
+    <t>Divyasri V</t>
+  </si>
+  <si>
+    <t>Donie Pepin B</t>
+  </si>
+  <si>
+    <t>Donyprakash R</t>
+  </si>
+  <si>
+    <t>Elamathi S</t>
+  </si>
+  <si>
+    <t>Franklin Raj B</t>
+  </si>
+  <si>
+    <t>Gaddam Gokul</t>
+  </si>
+  <si>
+    <t>Gagan Indrajith G S</t>
+  </si>
+  <si>
+    <t>Ganga Gowri P</t>
+  </si>
+  <si>
+    <t>Geetika Napa Munikumar</t>
+  </si>
+  <si>
+    <t>Gowthaman A</t>
+  </si>
+  <si>
+    <t>Gowthamraj G</t>
+  </si>
+  <si>
+    <t>Gunal B</t>
+  </si>
+  <si>
+    <t>Gunali A</t>
+  </si>
+  <si>
+    <t>Gurusharma C</t>
+  </si>
+  <si>
+    <t>Hari Ganesh R</t>
+  </si>
+  <si>
+    <t>Hari Hara Venkatesh K S</t>
+  </si>
+  <si>
+    <t>Hari Prasath
+Palanimurugan</t>
+  </si>
+  <si>
+    <t>Hariharan K</t>
+  </si>
+  <si>
+    <t>Harish J</t>
+  </si>
+  <si>
+    <t>Harish R</t>
+  </si>
+  <si>
+    <t>Harish V</t>
+  </si>
+  <si>
+    <t>Harsath Abinav M</t>
+  </si>
+  <si>
+    <t>Harshal Sai M</t>
+  </si>
+  <si>
+    <t>Harshan M</t>
+  </si>
+  <si>
+    <t>Hema Priya</t>
+  </si>
+  <si>
+    <t>Hema Priya Dharshini M</t>
+  </si>
+  <si>
+    <t>Hemanth M</t>
+  </si>
+  <si>
+    <t>Hemeshkumar Parthiban</t>
+  </si>
+  <si>
+    <t>Hrishivendan P</t>
+  </si>
+  <si>
+    <t>Humeshkumar K E</t>
+  </si>
+  <si>
+    <t>Indhuja P</t>
+  </si>
+  <si>
+    <t>Ishwariya R</t>
+  </si>
+  <si>
+    <t>Ishwarya L</t>
+  </si>
+  <si>
+    <t>Jaidev Arunachalam S</t>
+  </si>
+  <si>
+    <t>Jayasree D</t>
+  </si>
+  <si>
+    <t>B Jayasri</t>
+  </si>
+  <si>
+    <t>Jayasuriya J</t>
+  </si>
+  <si>
+    <t>Jebin Libni J</t>
+  </si>
+  <si>
+    <t>Jeeva S</t>
+  </si>
+  <si>
+    <t>Jeevan B K</t>
+  </si>
+  <si>
+    <t>Jeshwanth P</t>
+  </si>
+  <si>
+    <t>Jeya Surya J</t>
+  </si>
+  <si>
+    <t>Jeyaguru M</t>
+  </si>
+  <si>
+    <t>Jishnu Raj T R</t>
+  </si>
+  <si>
+    <t>Jothika K</t>
+  </si>
+  <si>
+    <t>Jyoshini Natesan
+Tamilselvan</t>
+  </si>
+  <si>
+    <t>Kaavya H</t>
+  </si>
+  <si>
+    <t>Kalvin S</t>
+  </si>
+  <si>
+    <t>Kamalesh V S</t>
+  </si>
+  <si>
+    <t>Karan Krishna C</t>
+  </si>
+  <si>
+    <t>Karthieswaran L</t>
+  </si>
+  <si>
+    <t>Kavimalar D</t>
+  </si>
+  <si>
+    <t>Kavin Prasad S</t>
+  </si>
+  <si>
+    <t>Kavin Raj S</t>
+  </si>
+  <si>
+    <t>Kavitha S</t>
+  </si>
+  <si>
+    <t>Keerthana P</t>
+  </si>
+  <si>
+    <t>Keerthana T</t>
+  </si>
+  <si>
+    <t>Keerthivasan S</t>
+  </si>
+  <si>
+    <t>Kishore Raj A S</t>
+  </si>
+  <si>
+    <t>Krithika Gopalakrishnan</t>
+  </si>
+  <si>
+    <t>Kumaran J</t>
+  </si>
+  <si>
+    <t>Lakshanika V S</t>
+  </si>
+  <si>
+    <t>Lakshitha K</t>
+  </si>
+  <si>
+    <t>Lakshmi Narayanan S</t>
+  </si>
+  <si>
+    <t>Lakshmi Shri S</t>
+  </si>
+  <si>
+    <t>Lathika N</t>
+  </si>
+  <si>
+    <t>Lejo C</t>
+  </si>
+  <si>
+    <t>Libin Koodananickal 
+Mathew</t>
+  </si>
+  <si>
+    <t>Lingesh Pandian S</t>
+  </si>
+  <si>
+    <t>Luqman T</t>
+  </si>
+  <si>
+    <t>Madhan Rasamalla 
+Venkatesalu</t>
+  </si>
+  <si>
+    <t>B Madhav</t>
+  </si>
+  <si>
+    <t>Madhumitha G</t>
+  </si>
+  <si>
+    <t>Madhumitha K</t>
+  </si>
+  <si>
+    <t>V P Madhumithaa</t>
+  </si>
+  <si>
+    <t>Mahathi A J</t>
+  </si>
+  <si>
+    <t>Mahesh K</t>
+  </si>
+  <si>
+    <t>Manju Sri N</t>
+  </si>
+  <si>
+    <t>Manoj P T</t>
+  </si>
+  <si>
+    <t>Manoj V</t>
+  </si>
+  <si>
+    <t>Meeghasree D</t>
+  </si>
+  <si>
+    <t>Meetha Dinesan</t>
+  </si>
+  <si>
+    <t>Mithun Chakravarthy L</t>
+  </si>
+  <si>
+    <t>Mithun K V</t>
+  </si>
+  <si>
+    <t>Mohamed Aadhil M</t>
+  </si>
+  <si>
+    <t>Mohamed Arafath K</t>
+  </si>
+  <si>
+    <t>Mohamed Fuzail A</t>
+  </si>
+  <si>
+    <t>Mohammed Aathil S</t>
+  </si>
+  <si>
+    <t>R Mohana Shri</t>
+  </si>
+  <si>
+    <t>Mohanasankari A</t>
+  </si>
+  <si>
+    <t>Mohanasundaram A</t>
+  </si>
+  <si>
+    <t>Monica K</t>
+  </si>
+  <si>
+    <t>Monish Raj R G</t>
+  </si>
+  <si>
+    <t>Monisha Dhar</t>
+  </si>
+  <si>
+    <t>Mukesh D</t>
+  </si>
+  <si>
+    <t>Muthu Sri Ram M</t>
+  </si>
+  <si>
+    <t>Muthukutti R</t>
+  </si>
+  <si>
+    <t>Mylesh A</t>
+  </si>
+  <si>
+    <t>Mythili S</t>
+  </si>
+  <si>
+    <t>Nabeela Meeral M</t>
+  </si>
+  <si>
+    <t>Nandana Pramod</t>
+  </si>
+  <si>
+    <t>Narmadha K</t>
+  </si>
+  <si>
+    <t>Naveen P</t>
+  </si>
+  <si>
+    <t>Naveen R</t>
+  </si>
+  <si>
+    <t>Nekhita Sri M</t>
+  </si>
+  <si>
+    <t>Nijanthan V</t>
+  </si>
+  <si>
+    <t>Nikithaa D</t>
+  </si>
+  <si>
+    <t>V Nishanthan</t>
+  </si>
+  <si>
+    <t>Nithin S</t>
+  </si>
+  <si>
+    <t>Nithish M</t>
+  </si>
+  <si>
+    <t>Nivass C R</t>
+  </si>
+  <si>
+    <t>Padmavathi M</t>
+  </si>
+  <si>
+    <t>Palachuru Nandu Priya</t>
+  </si>
+  <si>
+    <t>Pargavi S</t>
+  </si>
+  <si>
+    <t>P Pavishya</t>
+  </si>
+  <si>
+    <t>Pavithran M</t>
+  </si>
+  <si>
+    <t>Pooja S</t>
+  </si>
+  <si>
+    <t>Poojashree S</t>
+  </si>
+  <si>
+    <t>Poovitha K</t>
+  </si>
+  <si>
+    <t>POOVIZHI K</t>
+  </si>
+  <si>
+    <t>Pranav D L</t>
+  </si>
+  <si>
+    <t>Prasanna B</t>
+  </si>
+  <si>
+    <t>Prasanna Nadrajan R</t>
+  </si>
+  <si>
+    <t>Prathap T</t>
+  </si>
+  <si>
+    <t>Prathiba Umapathy</t>
+  </si>
+  <si>
+    <t>S Prathiksha</t>
+  </si>
+  <si>
+    <t>Praveen Kumar S</t>
+  </si>
+  <si>
+    <t>Praveen L</t>
+  </si>
+  <si>
+    <t>Pritika R</t>
+  </si>
+  <si>
+    <t>Priyanka S</t>
+  </si>
+  <si>
+    <t>Ragul P</t>
+  </si>
+  <si>
+    <t>Ragul R</t>
+  </si>
+  <si>
+    <t>Raguvarman M A</t>
+  </si>
+  <si>
+    <t>Ramkumar S S</t>
+  </si>
+  <si>
+    <t>Ranjani S</t>
+  </si>
+  <si>
+    <t>Rashiga B</t>
+  </si>
+  <si>
+    <t>Ravi Priyan R</t>
+  </si>
+  <si>
+    <t>Rena J</t>
+  </si>
+  <si>
+    <t>Rishikesh D</t>
+  </si>
+  <si>
+    <t>G Rithikaa</t>
+  </si>
+  <si>
+    <t>Rohan Chelliah S K</t>
+  </si>
+  <si>
+    <t>A Roshan</t>
+  </si>
+  <si>
+    <t>Roshin R G</t>
+  </si>
+  <si>
+    <t>Ruban Kumar R</t>
+  </si>
+  <si>
+    <t>Saalini P</t>
+  </si>
+  <si>
+    <t>Sadha Yuvarani Y</t>
+  </si>
+  <si>
+    <t>Sakthivel P</t>
+  </si>
+  <si>
+    <t>Sameer Ahamed S</t>
+  </si>
+  <si>
+    <t>Sanjay Ganesh V</t>
+  </si>
+  <si>
+    <t>S G Sanjay Kumar</t>
+  </si>
+  <si>
+    <t>Sanjay S</t>
+  </si>
+  <si>
+    <t>Sanjay V</t>
+  </si>
+  <si>
+    <t>Sanjeetha B</t>
+  </si>
+  <si>
+    <t>Santhosh S</t>
+  </si>
+  <si>
+    <t>Saqlain Ahamed Mothi 
+Ahamed</t>
+  </si>
+  <si>
+    <t>Saravana J M</t>
+  </si>
+  <si>
+    <t>Shalini Punithan</t>
+  </si>
+  <si>
+    <t>Shargeesh S</t>
+  </si>
+  <si>
+    <t>S Sharukesh</t>
+  </si>
+  <si>
+    <t>Shashwataarya M P</t>
+  </si>
+  <si>
+    <t>Shikha Ajith</t>
+  </si>
+  <si>
+    <t>Shree Harish V</t>
+  </si>
+  <si>
+    <t>Shruthe O</t>
+  </si>
+  <si>
+    <t>Shyam Ganesh D</t>
+  </si>
+  <si>
+    <t>Siddharth Radhakrishnan</t>
+  </si>
+  <si>
+    <t>Sivagopika M</t>
+  </si>
+  <si>
+    <t>Sri Durga R</t>
+  </si>
+  <si>
+    <t>Sriman A</t>
+  </si>
+  <si>
+    <t>Subha Sri S</t>
+  </si>
+  <si>
+    <t>Sudiksha S</t>
+  </si>
+  <si>
+    <t>Sugitha N</t>
+  </si>
+  <si>
+    <t>Sujit R</t>
+  </si>
+  <si>
+    <t>Sujitha Neelakandan
+Vigneshwari</t>
+  </si>
+  <si>
+    <t>Sunmathi S</t>
+  </si>
+  <si>
+    <t>Surya N</t>
+  </si>
+  <si>
+    <t>Suseendar Hari Krishnan</t>
+  </si>
+  <si>
+    <t>Swetha S</t>
+  </si>
+  <si>
+    <t>Syed Mohammed Hussain
+S</t>
+  </si>
+  <si>
+    <t>Tamilselvan K</t>
+  </si>
+  <si>
+    <t>Tarika A G</t>
+  </si>
+  <si>
+    <t>Tejeshwaran P</t>
+  </si>
+  <si>
+    <t>Tharun R K</t>
+  </si>
+  <si>
+    <t>Tharunika R</t>
+  </si>
+  <si>
+    <t>R Theppan Sanjay</t>
+  </si>
+  <si>
+    <t>Udhaya Karthikeyan N</t>
+  </si>
+  <si>
+    <t>Udhaya Krishna K G</t>
+  </si>
+  <si>
+    <t>Udhayaraj D</t>
+  </si>
+  <si>
+    <t>Ukirtha S</t>
+  </si>
+  <si>
+    <t>Vaishali P</t>
+  </si>
+  <si>
+    <t>Vandana M</t>
+  </si>
+  <si>
+    <t>Vengadesha Bharathi K</t>
+  </si>
+  <si>
+    <t>Venkat Krishna A</t>
+  </si>
+  <si>
+    <t>M Vetrichelvan</t>
+  </si>
+  <si>
+    <t>Vijay M</t>
+  </si>
+  <si>
+    <t>Vijay S</t>
+  </si>
+  <si>
+    <t>Vikashini M</t>
+  </si>
+  <si>
+    <t>Vishal Naresh R P</t>
+  </si>
+  <si>
+    <t>K S Vishruthi</t>
+  </si>
+  <si>
+    <t>Viswesh R K</t>
+  </si>
+  <si>
+    <t>Yadhra S</t>
+  </si>
+  <si>
+    <t>Yadhu Nandhana Ramesh
+Krishnan</t>
+  </si>
+  <si>
+    <t>Yarramsetty Venkat 
+Divyansh</t>
+  </si>
+  <si>
+    <t>Yogadharshini N K</t>
+  </si>
+  <si>
+    <t>Yogeetha A</t>
+  </si>
+  <si>
+    <t>Yokitha S</t>
+  </si>
+  <si>
+    <t>Zaina Raheen A P</t>
+  </si>
+  <si>
+    <t>Lakshan S</t>
+  </si>
+  <si>
+    <t>NANTHA KUMAR K</t>
+  </si>
+  <si>
+    <t>KARTHIKEYAN A</t>
+  </si>
+  <si>
+    <t>SANJAY N</t>
+  </si>
+  <si>
+    <t>ANBARASAN G</t>
+  </si>
+  <si>
+    <t>VIGNESH T</t>
+  </si>
+  <si>
+    <t>SUDHA V</t>
+  </si>
+  <si>
+    <t>GOKAL KANNA R</t>
+  </si>
+  <si>
+    <t>Design an HTML page for Employee Details with fields: Employee ID, Name, and Designation. Include four salary components: Basic Pay, DA, HRA, and Allowance. Use JavaScript to calculate and display total salary.</t>
+  </si>
+  <si>
+    <t>Design an HTML Registration page with fields: First Name, Last Name, Email ID, Password, Mobile Number, and Address. Include Submit and Reset buttons. Use JavaScript to validate all fields and display an alert if the form is submitted with empty fields.</t>
   </si>
 </sst>
 </file>
@@ -599,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D334"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -613,7 +1414,7 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
@@ -624,10 +1425,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>241801018</v>
+        <v>241801001</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="C2" t="s">
         <v>3</v>
@@ -638,13 +1439,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>241801027</v>
+        <v>241801002</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
@@ -652,13 +1453,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>241801029</v>
+        <v>241801003</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -666,13 +1467,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>241801038</v>
+        <v>241801004</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -680,10 +1481,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>241801042</v>
+        <v>241801005</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
         <v>4</v>
@@ -694,13 +1495,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>241801044</v>
+        <v>241801006</v>
       </c>
       <c r="B7" t="s">
-        <v>12</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -708,38 +1509,38 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>241801050</v>
+        <v>241801007</v>
       </c>
       <c r="B8" t="s">
-        <v>13</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
         <v>6</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>241801056</v>
+        <v>241801009</v>
       </c>
       <c r="B9" t="s">
-        <v>14</v>
+        <v>83</v>
       </c>
       <c r="C9" t="s">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>241801071</v>
+        <v>241801011</v>
       </c>
       <c r="B10" t="s">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -750,24 +1551,24 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>241801081</v>
+        <v>241801012</v>
       </c>
       <c r="B11" t="s">
-        <v>16</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>241801086</v>
+        <v>241801013</v>
       </c>
       <c r="B12" t="s">
-        <v>17</v>
+        <v>86</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
@@ -778,10 +1579,10 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>241801116</v>
+        <v>241801014</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="C13" t="s">
         <v>6</v>
@@ -792,27 +1593,27 @@
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>241801125</v>
+        <v>241801015</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>88</v>
       </c>
       <c r="C14" t="s">
         <v>5</v>
       </c>
       <c r="D14" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>241801126</v>
+        <v>241801016</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="C15" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D15" t="s">
         <v>3</v>
@@ -820,27 +1621,27 @@
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>241801130</v>
+        <v>241801017</v>
       </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>90</v>
       </c>
       <c r="C16" t="s">
         <v>5</v>
       </c>
       <c r="D16" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>241801139</v>
+        <v>241801018</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="C17" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D17" t="s">
         <v>3</v>
@@ -848,38 +1649,38 @@
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>241801140</v>
+        <v>241801019</v>
       </c>
       <c r="B18" t="s">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="C18" t="s">
         <v>4</v>
       </c>
       <c r="D18" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>241801142</v>
+        <v>241801020</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>92</v>
       </c>
       <c r="C19" t="s">
         <v>6</v>
       </c>
       <c r="D19" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>241801147</v>
+        <v>241801021</v>
       </c>
       <c r="B20" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="C20" t="s">
         <v>5</v>
@@ -890,13 +1691,13 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>241801150</v>
+        <v>241801022</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="D21" t="s">
         <v>3</v>
@@ -904,10 +1705,10 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>241801154</v>
+        <v>241801023</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>95</v>
       </c>
       <c r="C22" t="s">
         <v>3</v>
@@ -918,10 +1719,10 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>241801157</v>
+        <v>241801024</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="C23" t="s">
         <v>5</v>
@@ -932,41 +1733,41 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>241801163</v>
+        <v>241801025</v>
       </c>
       <c r="B24" t="s">
-        <v>29</v>
+        <v>97</v>
       </c>
       <c r="C24" t="s">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>241801165</v>
+        <v>241801026</v>
       </c>
       <c r="B25" t="s">
-        <v>30</v>
+        <v>98</v>
       </c>
       <c r="C25" t="s">
         <v>4</v>
       </c>
       <c r="D25" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26">
-        <v>241801166</v>
+        <v>241801027</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D26" t="s">
         <v>4</v>
@@ -974,13 +1775,13 @@
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>241801176</v>
+        <v>241801028</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>99</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D27" t="s">
         <v>3</v>
@@ -988,13 +1789,13 @@
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>241801187</v>
+        <v>241801029</v>
       </c>
       <c r="B28" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="D28" t="s">
         <v>5</v>
@@ -1002,27 +1803,27 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>241801188</v>
+        <v>241801030</v>
       </c>
       <c r="B29" t="s">
-        <v>34</v>
+        <v>100</v>
       </c>
       <c r="C29" t="s">
         <v>4</v>
       </c>
       <c r="D29" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>241801189</v>
+        <v>241801031</v>
       </c>
       <c r="B30" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="D30" t="s">
         <v>4</v>
@@ -1030,52 +1831,52 @@
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>241801197</v>
+        <v>241801032</v>
       </c>
       <c r="B31" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="C31" t="s">
         <v>5</v>
       </c>
       <c r="D31" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>241801204</v>
+        <v>241801033</v>
       </c>
       <c r="B32" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="C32" t="s">
         <v>6</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>241801211</v>
+        <v>241801034</v>
       </c>
       <c r="B33" t="s">
-        <v>38</v>
+        <v>104</v>
       </c>
       <c r="C33" t="s">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>241801214</v>
+        <v>241801035</v>
       </c>
       <c r="B34" t="s">
-        <v>39</v>
+        <v>105</v>
       </c>
       <c r="C34" t="s">
         <v>4</v>
@@ -1086,13 +1887,13 @@
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>241801215</v>
+        <v>241801036</v>
       </c>
       <c r="B35" t="s">
-        <v>40</v>
+        <v>106</v>
       </c>
       <c r="C35" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D35" t="s">
         <v>4</v>
@@ -1100,10 +1901,10 @@
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>241801218</v>
+        <v>241801038</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
         <v>4</v>
@@ -1114,13 +1915,13 @@
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>241801223</v>
+        <v>241801039</v>
       </c>
       <c r="B37" t="s">
-        <v>42</v>
+        <v>107</v>
       </c>
       <c r="C37" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="D37" t="s">
         <v>4</v>
@@ -1128,13 +1929,13 @@
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>241801231</v>
+        <v>241801040</v>
       </c>
       <c r="B38" t="s">
-        <v>43</v>
+        <v>108</v>
       </c>
       <c r="C38" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="D38" t="s">
         <v>6</v>
@@ -1142,13 +1943,13 @@
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>241801236</v>
+        <v>241801041</v>
       </c>
       <c r="B39" t="s">
-        <v>44</v>
+        <v>109</v>
       </c>
       <c r="C39" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D39" t="s">
         <v>4</v>
@@ -1156,38 +1957,38 @@
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>241801238</v>
+        <v>241801042</v>
       </c>
       <c r="B40" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="C40" t="s">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>241801239</v>
+        <v>241801043</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>110</v>
       </c>
       <c r="C41" t="s">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>241801242</v>
+        <v>241801044</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
       <c r="C42" t="s">
         <v>5</v>
@@ -1198,13 +1999,13 @@
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43">
-        <v>241801244</v>
+        <v>241801045</v>
       </c>
       <c r="B43" t="s">
-        <v>48</v>
+        <v>111</v>
       </c>
       <c r="C43" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D43" t="s">
         <v>3</v>
@@ -1212,13 +2013,13 @@
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>241801249</v>
+        <v>241801046</v>
       </c>
       <c r="B44" t="s">
-        <v>49</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D44" t="s">
         <v>5</v>
@@ -1226,10 +2027,10 @@
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>241801250</v>
+        <v>241801047</v>
       </c>
       <c r="B45" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="C45" t="s">
         <v>5</v>
@@ -1240,27 +2041,27 @@
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>241801254</v>
+        <v>241801048</v>
       </c>
       <c r="B46" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
       <c r="C46" t="s">
         <v>4</v>
       </c>
       <c r="D46" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47">
-        <v>241801255</v>
+        <v>241801049</v>
       </c>
       <c r="B47" t="s">
-        <v>52</v>
+        <v>115</v>
       </c>
       <c r="C47" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D47" t="s">
         <v>4</v>
@@ -1268,10 +2069,10 @@
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>241801256</v>
+        <v>241801050</v>
       </c>
       <c r="B48" t="s">
-        <v>53</v>
+        <v>13</v>
       </c>
       <c r="C48" t="s">
         <v>4</v>
@@ -1282,13 +2083,13 @@
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>241801257</v>
+        <v>241801051</v>
       </c>
       <c r="B49" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="C49" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D49" t="s">
         <v>3</v>
@@ -1296,66 +2097,66 @@
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50">
-        <v>241801262</v>
+        <v>241801052</v>
       </c>
       <c r="B50" t="s">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="C50" t="s">
         <v>4</v>
       </c>
       <c r="D50" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>241801267</v>
+        <v>241801053</v>
       </c>
       <c r="B51" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
       <c r="C51" t="s">
         <v>6</v>
       </c>
       <c r="D51" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52">
-        <v>241801268</v>
+        <v>241801054</v>
       </c>
       <c r="B52" t="s">
-        <v>57</v>
+        <v>119</v>
       </c>
       <c r="C52" t="s">
         <v>4</v>
       </c>
       <c r="D52" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53">
-        <v>241801270</v>
+        <v>241801055</v>
       </c>
       <c r="B53" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
       <c r="C53" t="s">
         <v>4</v>
       </c>
       <c r="D53" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54">
-        <v>241801272</v>
+        <v>241801056</v>
       </c>
       <c r="B54" t="s">
-        <v>59</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
         <v>3</v>
@@ -1366,38 +2167,38 @@
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55">
-        <v>241801274</v>
+        <v>241801057</v>
       </c>
       <c r="B55" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="C55" t="s">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56">
-        <v>241801275</v>
+        <v>241801058</v>
       </c>
       <c r="B56" t="s">
-        <v>61</v>
+        <v>122</v>
       </c>
       <c r="C56" t="s">
         <v>6</v>
       </c>
       <c r="D56" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57">
-        <v>241801281</v>
+        <v>241801059</v>
       </c>
       <c r="B57" t="s">
-        <v>62</v>
+        <v>123</v>
       </c>
       <c r="C57" t="s">
         <v>3</v>
@@ -1408,38 +2209,38 @@
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58">
-        <v>241801282</v>
+        <v>241801060</v>
       </c>
       <c r="B58" t="s">
-        <v>63</v>
+        <v>124</v>
       </c>
       <c r="C58" t="s">
         <v>5</v>
       </c>
       <c r="D58" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59">
-        <v>241801284</v>
+        <v>241801061</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
       <c r="C59" t="s">
         <v>6</v>
       </c>
       <c r="D59" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60">
-        <v>241801291</v>
+        <v>241801062</v>
       </c>
       <c r="B60" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="C60" t="s">
         <v>5</v>
@@ -1450,13 +2251,13 @@
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61">
-        <v>241801293</v>
+        <v>241801063</v>
       </c>
       <c r="B61" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="C61" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="D61" t="s">
         <v>5</v>
@@ -1464,13 +2265,13 @@
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62">
-        <v>241801294</v>
+        <v>241801064</v>
       </c>
       <c r="B62" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="C62" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D62" t="s">
         <v>6</v>
@@ -1478,24 +2279,24 @@
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63">
-        <v>241801297</v>
+        <v>241801065</v>
       </c>
       <c r="B63" t="s">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="C63" t="s">
         <v>5</v>
       </c>
       <c r="D63" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64">
-        <v>241801298</v>
+        <v>241801066</v>
       </c>
       <c r="B64" t="s">
-        <v>69</v>
+        <v>130</v>
       </c>
       <c r="C64" t="s">
         <v>5</v>
@@ -1506,13 +2307,13 @@
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65">
-        <v>241801300</v>
+        <v>241801067</v>
       </c>
       <c r="B65" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="C65" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D65" t="s">
         <v>5</v>
@@ -1520,24 +2321,24 @@
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66">
-        <v>241801310</v>
+        <v>241801068</v>
       </c>
       <c r="B66" t="s">
-        <v>71</v>
+        <v>132</v>
       </c>
       <c r="C66" t="s">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67">
-        <v>241801311</v>
+        <v>241801069</v>
       </c>
       <c r="B67" t="s">
-        <v>72</v>
+        <v>133</v>
       </c>
       <c r="C67" t="s">
         <v>4</v>
@@ -1548,13 +2349,13 @@
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68">
-        <v>241801315</v>
+        <v>241801070</v>
       </c>
       <c r="B68" t="s">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="C68" t="s">
-        <v>79</v>
+        <v>341</v>
       </c>
       <c r="D68" t="s">
         <v>3</v>
@@ -1562,10 +2363,10 @@
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69">
-        <v>241801317</v>
+        <v>241801071</v>
       </c>
       <c r="B69" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="C69" t="s">
         <v>6</v>
@@ -1576,13 +2377,13 @@
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70">
-        <v>241801323</v>
+        <v>241801072</v>
       </c>
       <c r="B70" t="s">
-        <v>75</v>
+        <v>135</v>
       </c>
       <c r="C70" t="s">
-        <v>78</v>
+        <v>342</v>
       </c>
       <c r="D70" t="s">
         <v>5</v>
@@ -1590,16 +2391,3698 @@
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71">
+        <v>241801073</v>
+      </c>
+      <c r="B71" t="s">
+        <v>136</v>
+      </c>
+      <c r="C71" t="s">
+        <v>341</v>
+      </c>
+      <c r="D71" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>241801074</v>
+      </c>
+      <c r="B72" t="s">
+        <v>137</v>
+      </c>
+      <c r="C72" t="s">
+        <v>3</v>
+      </c>
+      <c r="D72" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>241801075</v>
+      </c>
+      <c r="B73" t="s">
+        <v>138</v>
+      </c>
+      <c r="C73" t="s">
+        <v>341</v>
+      </c>
+      <c r="D73" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>241801076</v>
+      </c>
+      <c r="B74" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" t="s">
+        <v>342</v>
+      </c>
+      <c r="D74" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>241801077</v>
+      </c>
+      <c r="B75" t="s">
+        <v>140</v>
+      </c>
+      <c r="C75" t="s">
+        <v>341</v>
+      </c>
+      <c r="D75" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>241801078</v>
+      </c>
+      <c r="B76" t="s">
+        <v>141</v>
+      </c>
+      <c r="C76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>241801079</v>
+      </c>
+      <c r="B77" t="s">
+        <v>142</v>
+      </c>
+      <c r="C77" t="s">
+        <v>342</v>
+      </c>
+      <c r="D77" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>241801080</v>
+      </c>
+      <c r="B78" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>241801081</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="s">
+        <v>3</v>
+      </c>
+      <c r="D79" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>241801082</v>
+      </c>
+      <c r="B80" t="s">
+        <v>144</v>
+      </c>
+      <c r="C80" t="s">
+        <v>4</v>
+      </c>
+      <c r="D80" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>241801083</v>
+      </c>
+      <c r="B81" t="s">
+        <v>145</v>
+      </c>
+      <c r="C81" t="s">
+        <v>3</v>
+      </c>
+      <c r="D81" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>241801084</v>
+      </c>
+      <c r="B82" t="s">
+        <v>146</v>
+      </c>
+      <c r="C82" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>241801085</v>
+      </c>
+      <c r="B83" t="s">
+        <v>147</v>
+      </c>
+      <c r="C83" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>241801086</v>
+      </c>
+      <c r="B84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>241801087</v>
+      </c>
+      <c r="B85" t="s">
+        <v>148</v>
+      </c>
+      <c r="C85" t="s">
+        <v>341</v>
+      </c>
+      <c r="D85" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>241801088</v>
+      </c>
+      <c r="B86" t="s">
+        <v>149</v>
+      </c>
+      <c r="C86" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>241801089</v>
+      </c>
+      <c r="B87" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87" t="s">
+        <v>341</v>
+      </c>
+      <c r="D87" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>241801090</v>
+      </c>
+      <c r="B88" t="s">
+        <v>151</v>
+      </c>
+      <c r="C88" t="s">
+        <v>4</v>
+      </c>
+      <c r="D88" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>241801091</v>
+      </c>
+      <c r="B89" t="s">
+        <v>152</v>
+      </c>
+      <c r="C89" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>241801092</v>
+      </c>
+      <c r="B90" t="s">
+        <v>153</v>
+      </c>
+      <c r="C90" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>241801093</v>
+      </c>
+      <c r="B91" t="s">
+        <v>154</v>
+      </c>
+      <c r="C91" t="s">
+        <v>342</v>
+      </c>
+      <c r="D91" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>241801094</v>
+      </c>
+      <c r="B92" t="s">
+        <v>155</v>
+      </c>
+      <c r="C92" t="s">
+        <v>3</v>
+      </c>
+      <c r="D92" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>241801095</v>
+      </c>
+      <c r="B93" t="s">
+        <v>156</v>
+      </c>
+      <c r="C93" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>241801096</v>
+      </c>
+      <c r="B94" t="s">
+        <v>157</v>
+      </c>
+      <c r="C94" t="s">
+        <v>3</v>
+      </c>
+      <c r="D94" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>241801097</v>
+      </c>
+      <c r="B95" t="s">
+        <v>158</v>
+      </c>
+      <c r="C95" t="s">
+        <v>4</v>
+      </c>
+      <c r="D95" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>241801098</v>
+      </c>
+      <c r="B96" t="s">
+        <v>159</v>
+      </c>
+      <c r="C96" t="s">
+        <v>341</v>
+      </c>
+      <c r="D96" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>241801099</v>
+      </c>
+      <c r="B97" t="s">
+        <v>160</v>
+      </c>
+      <c r="C97" t="s">
+        <v>341</v>
+      </c>
+      <c r="D97" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>241801100</v>
+      </c>
+      <c r="B98" t="s">
+        <v>161</v>
+      </c>
+      <c r="C98" t="s">
+        <v>342</v>
+      </c>
+      <c r="D98" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>241801101</v>
+      </c>
+      <c r="B99" t="s">
+        <v>162</v>
+      </c>
+      <c r="C99" t="s">
+        <v>4</v>
+      </c>
+      <c r="D99" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>241801102</v>
+      </c>
+      <c r="B100" t="s">
+        <v>163</v>
+      </c>
+      <c r="C100" t="s">
+        <v>342</v>
+      </c>
+      <c r="D100" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>241801103</v>
+      </c>
+      <c r="B101" t="s">
+        <v>164</v>
+      </c>
+      <c r="C101" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>241801104</v>
+      </c>
+      <c r="B102" t="s">
+        <v>165</v>
+      </c>
+      <c r="C102" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>241801105</v>
+      </c>
+      <c r="B103" t="s">
+        <v>166</v>
+      </c>
+      <c r="C103" t="s">
+        <v>3</v>
+      </c>
+      <c r="D103" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>241801106</v>
+      </c>
+      <c r="B104" t="s">
+        <v>167</v>
+      </c>
+      <c r="C104" t="s">
+        <v>4</v>
+      </c>
+      <c r="D104" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>241801107</v>
+      </c>
+      <c r="B105" t="s">
+        <v>168</v>
+      </c>
+      <c r="C105" t="s">
+        <v>341</v>
+      </c>
+      <c r="D105" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>241801108</v>
+      </c>
+      <c r="B106" t="s">
+        <v>169</v>
+      </c>
+      <c r="C106" t="s">
+        <v>4</v>
+      </c>
+      <c r="D106" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>241801109</v>
+      </c>
+      <c r="B107" t="s">
+        <v>170</v>
+      </c>
+      <c r="C107" t="s">
+        <v>342</v>
+      </c>
+      <c r="D107" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>241801110</v>
+      </c>
+      <c r="B108" t="s">
+        <v>171</v>
+      </c>
+      <c r="C108" t="s">
+        <v>342</v>
+      </c>
+      <c r="D108" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>241801111</v>
+      </c>
+      <c r="B109" t="s">
+        <v>172</v>
+      </c>
+      <c r="C109" t="s">
+        <v>341</v>
+      </c>
+      <c r="D109" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>241801112</v>
+      </c>
+      <c r="B110" t="s">
+        <v>173</v>
+      </c>
+      <c r="C110" t="s">
+        <v>3</v>
+      </c>
+      <c r="D110" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>241801113</v>
+      </c>
+      <c r="B111" t="s">
+        <v>174</v>
+      </c>
+      <c r="C111" t="s">
+        <v>3</v>
+      </c>
+      <c r="D111" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>241801114</v>
+      </c>
+      <c r="B112" t="s">
+        <v>175</v>
+      </c>
+      <c r="C112" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>241801115</v>
+      </c>
+      <c r="B113" t="s">
+        <v>176</v>
+      </c>
+      <c r="C113" t="s">
+        <v>341</v>
+      </c>
+      <c r="D113" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>241801116</v>
+      </c>
+      <c r="B114" t="s">
+        <v>18</v>
+      </c>
+      <c r="C114" t="s">
+        <v>341</v>
+      </c>
+      <c r="D114" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>241801117</v>
+      </c>
+      <c r="B115" t="s">
+        <v>177</v>
+      </c>
+      <c r="C115" t="s">
+        <v>5</v>
+      </c>
+      <c r="D115" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>241801118</v>
+      </c>
+      <c r="B116" t="s">
+        <v>178</v>
+      </c>
+      <c r="C116" t="s">
+        <v>4</v>
+      </c>
+      <c r="D116" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>241801119</v>
+      </c>
+      <c r="B117" t="s">
+        <v>179</v>
+      </c>
+      <c r="C117" t="s">
+        <v>341</v>
+      </c>
+      <c r="D117" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>241801120</v>
+      </c>
+      <c r="B118" t="s">
+        <v>180</v>
+      </c>
+      <c r="C118" t="s">
+        <v>4</v>
+      </c>
+      <c r="D118" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>241801121</v>
+      </c>
+      <c r="B119" t="s">
+        <v>181</v>
+      </c>
+      <c r="C119" t="s">
+        <v>341</v>
+      </c>
+      <c r="D119" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>241801122</v>
+      </c>
+      <c r="B120" t="s">
+        <v>182</v>
+      </c>
+      <c r="C120" t="s">
+        <v>4</v>
+      </c>
+      <c r="D120" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>241801123</v>
+      </c>
+      <c r="B121" t="s">
+        <v>183</v>
+      </c>
+      <c r="C121" t="s">
+        <v>6</v>
+      </c>
+      <c r="D121" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>241801124</v>
+      </c>
+      <c r="B122" t="s">
+        <v>184</v>
+      </c>
+      <c r="C122" t="s">
+        <v>4</v>
+      </c>
+      <c r="D122" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>241801125</v>
+      </c>
+      <c r="B123" t="s">
+        <v>19</v>
+      </c>
+      <c r="C123" t="s">
+        <v>4</v>
+      </c>
+      <c r="D123" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>241801126</v>
+      </c>
+      <c r="B124" t="s">
+        <v>20</v>
+      </c>
+      <c r="C124" t="s">
+        <v>3</v>
+      </c>
+      <c r="D124" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A125">
+        <v>241801127</v>
+      </c>
+      <c r="B125" t="s">
+        <v>185</v>
+      </c>
+      <c r="C125" t="s">
+        <v>3</v>
+      </c>
+      <c r="D125" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A126">
+        <v>241801128</v>
+      </c>
+      <c r="B126" t="s">
+        <v>186</v>
+      </c>
+      <c r="C126" t="s">
+        <v>6</v>
+      </c>
+      <c r="D126" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A127">
+        <v>241801129</v>
+      </c>
+      <c r="B127" t="s">
+        <v>187</v>
+      </c>
+      <c r="C127" t="s">
+        <v>3</v>
+      </c>
+      <c r="D127" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A128">
+        <v>241801130</v>
+      </c>
+      <c r="B128" t="s">
+        <v>21</v>
+      </c>
+      <c r="C128" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A129">
+        <v>241801131</v>
+      </c>
+      <c r="B129" t="s">
+        <v>188</v>
+      </c>
+      <c r="C129" t="s">
+        <v>6</v>
+      </c>
+      <c r="D129" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A130">
+        <v>241801132</v>
+      </c>
+      <c r="B130" t="s">
+        <v>189</v>
+      </c>
+      <c r="C130" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A131">
+        <v>241801133</v>
+      </c>
+      <c r="B131" t="s">
+        <v>190</v>
+      </c>
+      <c r="C131" t="s">
+        <v>342</v>
+      </c>
+      <c r="D131" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A132">
+        <v>241801134</v>
+      </c>
+      <c r="B132" t="s">
+        <v>191</v>
+      </c>
+      <c r="C132" t="s">
+        <v>341</v>
+      </c>
+      <c r="D132" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A133">
+        <v>241801135</v>
+      </c>
+      <c r="B133" t="s">
+        <v>192</v>
+      </c>
+      <c r="C133" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A134">
+        <v>241801136</v>
+      </c>
+      <c r="B134" t="s">
+        <v>193</v>
+      </c>
+      <c r="C134" t="s">
+        <v>5</v>
+      </c>
+      <c r="D134" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A135">
+        <v>241801137</v>
+      </c>
+      <c r="B135" t="s">
+        <v>194</v>
+      </c>
+      <c r="C135" t="s">
+        <v>341</v>
+      </c>
+      <c r="D135" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A136">
+        <v>241801138</v>
+      </c>
+      <c r="B136" t="s">
+        <v>195</v>
+      </c>
+      <c r="C136" t="s">
+        <v>3</v>
+      </c>
+      <c r="D136" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A137">
+        <v>241801139</v>
+      </c>
+      <c r="B137" t="s">
+        <v>22</v>
+      </c>
+      <c r="C137" t="s">
+        <v>4</v>
+      </c>
+      <c r="D137" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A138">
+        <v>241801140</v>
+      </c>
+      <c r="B138" t="s">
+        <v>23</v>
+      </c>
+      <c r="C138" t="s">
+        <v>341</v>
+      </c>
+      <c r="D138" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A139">
+        <v>241801141</v>
+      </c>
+      <c r="B139" t="s">
+        <v>196</v>
+      </c>
+      <c r="C139" t="s">
+        <v>6</v>
+      </c>
+      <c r="D139" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A140">
+        <v>241801142</v>
+      </c>
+      <c r="B140" t="s">
+        <v>197</v>
+      </c>
+      <c r="C140" t="s">
+        <v>342</v>
+      </c>
+      <c r="D140" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A141">
+        <v>241801143</v>
+      </c>
+      <c r="B141" t="s">
+        <v>198</v>
+      </c>
+      <c r="C141" t="s">
+        <v>341</v>
+      </c>
+      <c r="D141" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A142">
+        <v>241801144</v>
+      </c>
+      <c r="B142" t="s">
+        <v>199</v>
+      </c>
+      <c r="C142" t="s">
+        <v>3</v>
+      </c>
+      <c r="D142" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A143">
+        <v>241801145</v>
+      </c>
+      <c r="B143" t="s">
+        <v>200</v>
+      </c>
+      <c r="C143" t="s">
+        <v>341</v>
+      </c>
+      <c r="D143" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A144">
+        <v>241801146</v>
+      </c>
+      <c r="B144" t="s">
+        <v>201</v>
+      </c>
+      <c r="C144" t="s">
+        <v>342</v>
+      </c>
+      <c r="D144" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A145">
+        <v>241801147</v>
+      </c>
+      <c r="B145" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" t="s">
+        <v>341</v>
+      </c>
+      <c r="D145" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A146">
+        <v>241801148</v>
+      </c>
+      <c r="B146" t="s">
+        <v>202</v>
+      </c>
+      <c r="C146" t="s">
+        <v>4</v>
+      </c>
+      <c r="D146" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A147">
+        <v>241801149</v>
+      </c>
+      <c r="B147" t="s">
+        <v>203</v>
+      </c>
+      <c r="C147" t="s">
+        <v>342</v>
+      </c>
+      <c r="D147" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A148">
+        <v>241801150</v>
+      </c>
+      <c r="B148" t="s">
+        <v>25</v>
+      </c>
+      <c r="C148" t="s">
+        <v>6</v>
+      </c>
+      <c r="D148" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A149">
+        <v>241801151</v>
+      </c>
+      <c r="B149" t="s">
+        <v>204</v>
+      </c>
+      <c r="C149" t="s">
+        <v>3</v>
+      </c>
+      <c r="D149" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A150">
+        <v>241801152</v>
+      </c>
+      <c r="B150" t="s">
+        <v>205</v>
+      </c>
+      <c r="C150" t="s">
+        <v>4</v>
+      </c>
+      <c r="D150" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A151">
+        <v>241801153</v>
+      </c>
+      <c r="B151" t="s">
+        <v>206</v>
+      </c>
+      <c r="C151" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A152">
+        <v>241801154</v>
+      </c>
+      <c r="B152" t="s">
+        <v>26</v>
+      </c>
+      <c r="C152" t="s">
+        <v>5</v>
+      </c>
+      <c r="D152" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A153">
+        <v>241801155</v>
+      </c>
+      <c r="B153" t="s">
+        <v>207</v>
+      </c>
+      <c r="C153" t="s">
+        <v>6</v>
+      </c>
+      <c r="D153" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A154">
+        <v>241801156</v>
+      </c>
+      <c r="B154" t="s">
+        <v>208</v>
+      </c>
+      <c r="C154" t="s">
+        <v>5</v>
+      </c>
+      <c r="D154" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A155">
+        <v>241801157</v>
+      </c>
+      <c r="B155" t="s">
+        <v>27</v>
+      </c>
+      <c r="C155" t="s">
+        <v>341</v>
+      </c>
+      <c r="D155" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A156">
+        <v>241801158</v>
+      </c>
+      <c r="B156" t="s">
+        <v>209</v>
+      </c>
+      <c r="C156" t="s">
+        <v>5</v>
+      </c>
+      <c r="D156" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A157">
+        <v>241801159</v>
+      </c>
+      <c r="B157" t="s">
+        <v>210</v>
+      </c>
+      <c r="C157" t="s">
+        <v>341</v>
+      </c>
+      <c r="D157" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A158">
+        <v>241801160</v>
+      </c>
+      <c r="B158" t="s">
+        <v>211</v>
+      </c>
+      <c r="C158" t="s">
+        <v>4</v>
+      </c>
+      <c r="D158" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A159">
+        <v>241801161</v>
+      </c>
+      <c r="B159" t="s">
+        <v>212</v>
+      </c>
+      <c r="C159" t="s">
+        <v>6</v>
+      </c>
+      <c r="D159" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A160">
+        <v>241801162</v>
+      </c>
+      <c r="B160" t="s">
+        <v>213</v>
+      </c>
+      <c r="C160" t="s">
+        <v>5</v>
+      </c>
+      <c r="D160" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A161">
+        <v>241801163</v>
+      </c>
+      <c r="B161" t="s">
+        <v>28</v>
+      </c>
+      <c r="C161" t="s">
+        <v>342</v>
+      </c>
+      <c r="D161" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A162">
+        <v>241801164</v>
+      </c>
+      <c r="B162" t="s">
+        <v>214</v>
+      </c>
+      <c r="C162" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A163">
+        <v>241801165</v>
+      </c>
+      <c r="B163" t="s">
+        <v>29</v>
+      </c>
+      <c r="C163" t="s">
+        <v>5</v>
+      </c>
+      <c r="D163" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A164">
+        <v>241801166</v>
+      </c>
+      <c r="B164" t="s">
+        <v>30</v>
+      </c>
+      <c r="C164" t="s">
+        <v>3</v>
+      </c>
+      <c r="D164" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A165">
+        <v>241801167</v>
+      </c>
+      <c r="B165" t="s">
+        <v>215</v>
+      </c>
+      <c r="C165" t="s">
+        <v>4</v>
+      </c>
+      <c r="D165" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A166">
+        <v>241801168</v>
+      </c>
+      <c r="B166" t="s">
+        <v>216</v>
+      </c>
+      <c r="C166" t="s">
+        <v>341</v>
+      </c>
+      <c r="D166" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A167">
+        <v>241801169</v>
+      </c>
+      <c r="B167" t="s">
+        <v>217</v>
+      </c>
+      <c r="C167" t="s">
+        <v>341</v>
+      </c>
+      <c r="D167" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A168">
+        <v>241801170</v>
+      </c>
+      <c r="B168" t="s">
+        <v>218</v>
+      </c>
+      <c r="C168" t="s">
+        <v>342</v>
+      </c>
+      <c r="D168" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A169">
+        <v>241801171</v>
+      </c>
+      <c r="B169" t="s">
+        <v>219</v>
+      </c>
+      <c r="C169" t="s">
+        <v>4</v>
+      </c>
+      <c r="D169" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A170">
+        <v>241801172</v>
+      </c>
+      <c r="B170" t="s">
+        <v>220</v>
+      </c>
+      <c r="C170" t="s">
+        <v>342</v>
+      </c>
+      <c r="D170" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A171">
+        <v>241801173</v>
+      </c>
+      <c r="B171" t="s">
+        <v>221</v>
+      </c>
+      <c r="C171" t="s">
+        <v>5</v>
+      </c>
+      <c r="D171" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A172">
+        <v>241801174</v>
+      </c>
+      <c r="B172" t="s">
+        <v>222</v>
+      </c>
+      <c r="C172" t="s">
+        <v>6</v>
+      </c>
+      <c r="D172" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A173">
+        <v>241801175</v>
+      </c>
+      <c r="B173" t="s">
+        <v>223</v>
+      </c>
+      <c r="C173" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A174">
+        <v>241801176</v>
+      </c>
+      <c r="B174" t="s">
+        <v>31</v>
+      </c>
+      <c r="C174" t="s">
+        <v>4</v>
+      </c>
+      <c r="D174" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A175">
+        <v>241801177</v>
+      </c>
+      <c r="B175" t="s">
+        <v>224</v>
+      </c>
+      <c r="C175" t="s">
+        <v>341</v>
+      </c>
+      <c r="D175" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A176">
+        <v>241801178</v>
+      </c>
+      <c r="B176" t="s">
+        <v>225</v>
+      </c>
+      <c r="C176" t="s">
+        <v>4</v>
+      </c>
+      <c r="D176" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A177">
+        <v>241801179</v>
+      </c>
+      <c r="B177" t="s">
+        <v>226</v>
+      </c>
+      <c r="C177" t="s">
+        <v>342</v>
+      </c>
+      <c r="D177" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A178">
+        <v>241801180</v>
+      </c>
+      <c r="B178" t="s">
+        <v>227</v>
+      </c>
+      <c r="C178" t="s">
+        <v>342</v>
+      </c>
+      <c r="D178" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A179">
+        <v>241801181</v>
+      </c>
+      <c r="B179" t="s">
+        <v>228</v>
+      </c>
+      <c r="C179" t="s">
+        <v>341</v>
+      </c>
+      <c r="D179" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A180">
+        <v>241801182</v>
+      </c>
+      <c r="B180" t="s">
+        <v>229</v>
+      </c>
+      <c r="C180" t="s">
+        <v>3</v>
+      </c>
+      <c r="D180" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A181">
+        <v>241801183</v>
+      </c>
+      <c r="B181" t="s">
+        <v>230</v>
+      </c>
+      <c r="C181" t="s">
+        <v>3</v>
+      </c>
+      <c r="D181" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A182">
+        <v>241801184</v>
+      </c>
+      <c r="B182" t="s">
+        <v>231</v>
+      </c>
+      <c r="C182" t="s">
+        <v>5</v>
+      </c>
+      <c r="D182" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A183">
+        <v>241801185</v>
+      </c>
+      <c r="B183" t="s">
+        <v>232</v>
+      </c>
+      <c r="C183" t="s">
+        <v>341</v>
+      </c>
+      <c r="D183" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A184">
+        <v>241801186</v>
+      </c>
+      <c r="B184" t="s">
+        <v>233</v>
+      </c>
+      <c r="C184" t="s">
+        <v>341</v>
+      </c>
+      <c r="D184" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A185">
+        <v>241801187</v>
+      </c>
+      <c r="B185" t="s">
+        <v>32</v>
+      </c>
+      <c r="C185" t="s">
+        <v>5</v>
+      </c>
+      <c r="D185" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A186">
+        <v>241801188</v>
+      </c>
+      <c r="B186" t="s">
+        <v>33</v>
+      </c>
+      <c r="C186" t="s">
+        <v>4</v>
+      </c>
+      <c r="D186" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A187">
+        <v>241801189</v>
+      </c>
+      <c r="B187" t="s">
+        <v>34</v>
+      </c>
+      <c r="C187" t="s">
+        <v>341</v>
+      </c>
+      <c r="D187" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A188">
+        <v>241801190</v>
+      </c>
+      <c r="B188" t="s">
+        <v>234</v>
+      </c>
+      <c r="C188" t="s">
+        <v>4</v>
+      </c>
+      <c r="D188" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A189">
+        <v>241801191</v>
+      </c>
+      <c r="B189" t="s">
+        <v>235</v>
+      </c>
+      <c r="C189" t="s">
+        <v>341</v>
+      </c>
+      <c r="D189" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A190">
+        <v>241801192</v>
+      </c>
+      <c r="B190" t="s">
+        <v>236</v>
+      </c>
+      <c r="C190" t="s">
+        <v>4</v>
+      </c>
+      <c r="D190" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A191">
+        <v>241801193</v>
+      </c>
+      <c r="B191" t="s">
+        <v>237</v>
+      </c>
+      <c r="C191" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A192">
+        <v>241801194</v>
+      </c>
+      <c r="B192" t="s">
+        <v>238</v>
+      </c>
+      <c r="C192" t="s">
+        <v>4</v>
+      </c>
+      <c r="D192" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A193">
+        <v>241801195</v>
+      </c>
+      <c r="B193" t="s">
+        <v>239</v>
+      </c>
+      <c r="C193" t="s">
+        <v>4</v>
+      </c>
+      <c r="D193" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A194">
+        <v>241801196</v>
+      </c>
+      <c r="B194" t="s">
+        <v>240</v>
+      </c>
+      <c r="C194" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A195">
+        <v>241801197</v>
+      </c>
+      <c r="B195" t="s">
+        <v>35</v>
+      </c>
+      <c r="C195" t="s">
+        <v>3</v>
+      </c>
+      <c r="D195" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A196">
+        <v>241801198</v>
+      </c>
+      <c r="B196" t="s">
+        <v>241</v>
+      </c>
+      <c r="C196" t="s">
+        <v>6</v>
+      </c>
+      <c r="D196" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A197">
+        <v>241801199</v>
+      </c>
+      <c r="B197" t="s">
+        <v>242</v>
+      </c>
+      <c r="C197" t="s">
+        <v>3</v>
+      </c>
+      <c r="D197" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A198">
+        <v>241801200</v>
+      </c>
+      <c r="B198" t="s">
+        <v>243</v>
+      </c>
+      <c r="C198" t="s">
+        <v>5</v>
+      </c>
+      <c r="D198" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A199">
+        <v>241801201</v>
+      </c>
+      <c r="B199" t="s">
+        <v>244</v>
+      </c>
+      <c r="C199" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A200">
+        <v>241801202</v>
+      </c>
+      <c r="B200" t="s">
+        <v>245</v>
+      </c>
+      <c r="C200" t="s">
+        <v>5</v>
+      </c>
+      <c r="D200" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A201">
+        <v>241801203</v>
+      </c>
+      <c r="B201" t="s">
+        <v>246</v>
+      </c>
+      <c r="C201" t="s">
+        <v>342</v>
+      </c>
+      <c r="D201" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A202">
+        <v>241801204</v>
+      </c>
+      <c r="B202" t="s">
+        <v>36</v>
+      </c>
+      <c r="C202" t="s">
+        <v>341</v>
+      </c>
+      <c r="D202" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A203">
+        <v>241801205</v>
+      </c>
+      <c r="B203" t="s">
+        <v>247</v>
+      </c>
+      <c r="C203" t="s">
+        <v>5</v>
+      </c>
+      <c r="D203" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A204">
+        <v>241801206</v>
+      </c>
+      <c r="B204" t="s">
+        <v>248</v>
+      </c>
+      <c r="C204" t="s">
+        <v>5</v>
+      </c>
+      <c r="D204" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A205">
+        <v>241801207</v>
+      </c>
+      <c r="B205" t="s">
+        <v>249</v>
+      </c>
+      <c r="C205" t="s">
+        <v>341</v>
+      </c>
+      <c r="D205" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A206">
+        <v>241801208</v>
+      </c>
+      <c r="B206" t="s">
+        <v>250</v>
+      </c>
+      <c r="C206" t="s">
+        <v>3</v>
+      </c>
+      <c r="D206" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A207">
+        <v>241801209</v>
+      </c>
+      <c r="B207" t="s">
+        <v>251</v>
+      </c>
+      <c r="C207" t="s">
+        <v>4</v>
+      </c>
+      <c r="D207" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A208">
+        <v>241801210</v>
+      </c>
+      <c r="B208" t="s">
+        <v>252</v>
+      </c>
+      <c r="C208" t="s">
+        <v>341</v>
+      </c>
+      <c r="D208" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A209">
+        <v>241801211</v>
+      </c>
+      <c r="B209" t="s">
+        <v>37</v>
+      </c>
+      <c r="C209" t="s">
+        <v>6</v>
+      </c>
+      <c r="D209" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A210">
+        <v>241801212</v>
+      </c>
+      <c r="B210" t="s">
+        <v>253</v>
+      </c>
+      <c r="C210" t="s">
+        <v>342</v>
+      </c>
+      <c r="D210" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A211">
+        <v>241801213</v>
+      </c>
+      <c r="B211" t="s">
+        <v>254</v>
+      </c>
+      <c r="C211" t="s">
+        <v>341</v>
+      </c>
+      <c r="D211" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A212">
+        <v>241801214</v>
+      </c>
+      <c r="B212" t="s">
+        <v>38</v>
+      </c>
+      <c r="C212" t="s">
+        <v>3</v>
+      </c>
+      <c r="D212" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A213">
+        <v>241801215</v>
+      </c>
+      <c r="B213" t="s">
+        <v>39</v>
+      </c>
+      <c r="C213" t="s">
+        <v>341</v>
+      </c>
+      <c r="D213" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A214">
+        <v>241801216</v>
+      </c>
+      <c r="B214" t="s">
+        <v>255</v>
+      </c>
+      <c r="C214" t="s">
+        <v>342</v>
+      </c>
+      <c r="D214" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A215">
+        <v>241801217</v>
+      </c>
+      <c r="B215" t="s">
+        <v>256</v>
+      </c>
+      <c r="C215" t="s">
+        <v>341</v>
+      </c>
+      <c r="D215" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A216">
+        <v>241801218</v>
+      </c>
+      <c r="B216" t="s">
+        <v>40</v>
+      </c>
+      <c r="C216" t="s">
+        <v>4</v>
+      </c>
+      <c r="D216" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A217">
+        <v>241801219</v>
+      </c>
+      <c r="B217" t="s">
+        <v>257</v>
+      </c>
+      <c r="C217" t="s">
+        <v>342</v>
+      </c>
+      <c r="D217" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A218">
+        <v>241801220</v>
+      </c>
+      <c r="B218" t="s">
+        <v>258</v>
+      </c>
+      <c r="C218" t="s">
+        <v>6</v>
+      </c>
+      <c r="D218" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A219">
+        <v>241801221</v>
+      </c>
+      <c r="B219" t="s">
+        <v>259</v>
+      </c>
+      <c r="C219" t="s">
+        <v>3</v>
+      </c>
+      <c r="D219" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A220">
+        <v>241801222</v>
+      </c>
+      <c r="B220" t="s">
+        <v>260</v>
+      </c>
+      <c r="C220" t="s">
+        <v>4</v>
+      </c>
+      <c r="D220" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A221">
+        <v>241801223</v>
+      </c>
+      <c r="B221" t="s">
+        <v>41</v>
+      </c>
+      <c r="C221" t="s">
+        <v>3</v>
+      </c>
+      <c r="D221" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A222">
+        <v>241801224</v>
+      </c>
+      <c r="B222" t="s">
+        <v>261</v>
+      </c>
+      <c r="C222" t="s">
+        <v>5</v>
+      </c>
+      <c r="D222" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A223">
+        <v>241801225</v>
+      </c>
+      <c r="B223" t="s">
+        <v>262</v>
+      </c>
+      <c r="C223" t="s">
+        <v>6</v>
+      </c>
+      <c r="D223" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A224">
+        <v>241801226</v>
+      </c>
+      <c r="B224" t="s">
+        <v>263</v>
+      </c>
+      <c r="C224" t="s">
+        <v>5</v>
+      </c>
+      <c r="D224" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A225">
+        <v>241801227</v>
+      </c>
+      <c r="B225" t="s">
+        <v>264</v>
+      </c>
+      <c r="C225" t="s">
+        <v>341</v>
+      </c>
+      <c r="D225" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A226">
+        <v>241801228</v>
+      </c>
+      <c r="B226" t="s">
+        <v>265</v>
+      </c>
+      <c r="C226" t="s">
+        <v>5</v>
+      </c>
+      <c r="D226" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A227">
+        <v>241801229</v>
+      </c>
+      <c r="B227" t="s">
+        <v>266</v>
+      </c>
+      <c r="C227" t="s">
+        <v>341</v>
+      </c>
+      <c r="D227" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A228">
+        <v>241801230</v>
+      </c>
+      <c r="B228" t="s">
+        <v>267</v>
+      </c>
+      <c r="C228" t="s">
+        <v>4</v>
+      </c>
+      <c r="D228" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A229">
+        <v>241801231</v>
+      </c>
+      <c r="B229" t="s">
+        <v>42</v>
+      </c>
+      <c r="C229" t="s">
+        <v>6</v>
+      </c>
+      <c r="D229" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A230">
+        <v>241801232</v>
+      </c>
+      <c r="B230" t="s">
+        <v>268</v>
+      </c>
+      <c r="C230" t="s">
+        <v>5</v>
+      </c>
+      <c r="D230" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A231">
+        <v>241801233</v>
+      </c>
+      <c r="B231" t="s">
+        <v>269</v>
+      </c>
+      <c r="C231" t="s">
+        <v>342</v>
+      </c>
+      <c r="D231" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A232">
+        <v>241801234</v>
+      </c>
+      <c r="B232" t="s">
+        <v>270</v>
+      </c>
+      <c r="C232" t="s">
+        <v>3</v>
+      </c>
+      <c r="D232" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A233">
+        <v>241801235</v>
+      </c>
+      <c r="B233" t="s">
+        <v>271</v>
+      </c>
+      <c r="C233" t="s">
+        <v>5</v>
+      </c>
+      <c r="D233" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A234">
+        <v>241801236</v>
+      </c>
+      <c r="B234" t="s">
+        <v>43</v>
+      </c>
+      <c r="C234" t="s">
+        <v>3</v>
+      </c>
+      <c r="D234" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A235">
+        <v>241801237</v>
+      </c>
+      <c r="B235" t="s">
+        <v>272</v>
+      </c>
+      <c r="C235" t="s">
+        <v>4</v>
+      </c>
+      <c r="D235" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A236">
+        <v>241801238</v>
+      </c>
+      <c r="B236" t="s">
+        <v>44</v>
+      </c>
+      <c r="C236" t="s">
+        <v>341</v>
+      </c>
+      <c r="D236" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A237">
+        <v>241801239</v>
+      </c>
+      <c r="B237" t="s">
+        <v>45</v>
+      </c>
+      <c r="C237" t="s">
+        <v>341</v>
+      </c>
+      <c r="D237" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A238">
+        <v>241801240</v>
+      </c>
+      <c r="B238" t="s">
+        <v>273</v>
+      </c>
+      <c r="C238" t="s">
+        <v>342</v>
+      </c>
+      <c r="D238" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A239">
+        <v>241801241</v>
+      </c>
+      <c r="B239" t="s">
+        <v>274</v>
+      </c>
+      <c r="C239" t="s">
+        <v>4</v>
+      </c>
+      <c r="D239" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A240">
+        <v>241801242</v>
+      </c>
+      <c r="B240" t="s">
+        <v>46</v>
+      </c>
+      <c r="C240" t="s">
+        <v>342</v>
+      </c>
+      <c r="D240" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A241">
+        <v>241801243</v>
+      </c>
+      <c r="B241" t="s">
+        <v>275</v>
+      </c>
+      <c r="C241" t="s">
+        <v>5</v>
+      </c>
+      <c r="D241" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A242">
+        <v>241801244</v>
+      </c>
+      <c r="B242" t="s">
+        <v>47</v>
+      </c>
+      <c r="C242" t="s">
+        <v>6</v>
+      </c>
+      <c r="D242" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A243">
+        <v>241801245</v>
+      </c>
+      <c r="B243" t="s">
+        <v>276</v>
+      </c>
+      <c r="C243" t="s">
+        <v>3</v>
+      </c>
+      <c r="D243" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A244">
+        <v>241801246</v>
+      </c>
+      <c r="B244" t="s">
+        <v>277</v>
+      </c>
+      <c r="C244" t="s">
+        <v>4</v>
+      </c>
+      <c r="D244" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A245">
+        <v>241801247</v>
+      </c>
+      <c r="B245" t="s">
+        <v>278</v>
+      </c>
+      <c r="C245" t="s">
+        <v>341</v>
+      </c>
+      <c r="D245" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A246">
+        <v>241801248</v>
+      </c>
+      <c r="B246" t="s">
+        <v>279</v>
+      </c>
+      <c r="C246" t="s">
+        <v>4</v>
+      </c>
+      <c r="D246" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A247">
+        <v>241801249</v>
+      </c>
+      <c r="B247" t="s">
+        <v>48</v>
+      </c>
+      <c r="C247" t="s">
+        <v>342</v>
+      </c>
+      <c r="D247" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A248">
+        <v>241801250</v>
+      </c>
+      <c r="B248" t="s">
+        <v>49</v>
+      </c>
+      <c r="C248" t="s">
+        <v>342</v>
+      </c>
+      <c r="D248" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A249">
+        <v>241801251</v>
+      </c>
+      <c r="B249" t="s">
+        <v>280</v>
+      </c>
+      <c r="C249" t="s">
+        <v>341</v>
+      </c>
+      <c r="D249" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A250">
+        <v>241801252</v>
+      </c>
+      <c r="B250" t="s">
+        <v>281</v>
+      </c>
+      <c r="C250" t="s">
+        <v>3</v>
+      </c>
+      <c r="D250" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A251">
+        <v>241801253</v>
+      </c>
+      <c r="B251" t="s">
+        <v>282</v>
+      </c>
+      <c r="C251" t="s">
+        <v>3</v>
+      </c>
+      <c r="D251" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A252">
+        <v>241801254</v>
+      </c>
+      <c r="B252" t="s">
+        <v>50</v>
+      </c>
+      <c r="C252" t="s">
+        <v>5</v>
+      </c>
+      <c r="D252" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A253">
+        <v>241801255</v>
+      </c>
+      <c r="B253" t="s">
+        <v>51</v>
+      </c>
+      <c r="C253" t="s">
+        <v>341</v>
+      </c>
+      <c r="D253" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A254">
+        <v>241801256</v>
+      </c>
+      <c r="B254" t="s">
+        <v>52</v>
+      </c>
+      <c r="C254" t="s">
+        <v>341</v>
+      </c>
+      <c r="D254" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A255">
+        <v>241801257</v>
+      </c>
+      <c r="B255" t="s">
+        <v>53</v>
+      </c>
+      <c r="C255" t="s">
+        <v>5</v>
+      </c>
+      <c r="D255" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A256">
+        <v>241801258</v>
+      </c>
+      <c r="B256" t="s">
+        <v>283</v>
+      </c>
+      <c r="C256" t="s">
+        <v>4</v>
+      </c>
+      <c r="D256" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A257">
+        <v>241801259</v>
+      </c>
+      <c r="B257" t="s">
+        <v>284</v>
+      </c>
+      <c r="C257" t="s">
+        <v>341</v>
+      </c>
+      <c r="D257" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A258">
+        <v>241801260</v>
+      </c>
+      <c r="B258" t="s">
+        <v>285</v>
+      </c>
+      <c r="C258" t="s">
+        <v>4</v>
+      </c>
+      <c r="D258" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A259">
+        <v>241801261</v>
+      </c>
+      <c r="B259" t="s">
+        <v>286</v>
+      </c>
+      <c r="C259" t="s">
+        <v>341</v>
+      </c>
+      <c r="D259" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A260">
+        <v>241801262</v>
+      </c>
+      <c r="B260" t="s">
+        <v>54</v>
+      </c>
+      <c r="C260" t="s">
+        <v>4</v>
+      </c>
+      <c r="D260" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A261">
+        <v>241801263</v>
+      </c>
+      <c r="B261" t="s">
+        <v>287</v>
+      </c>
+      <c r="C261" t="s">
+        <v>6</v>
+      </c>
+      <c r="D261" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A262">
+        <v>241801264</v>
+      </c>
+      <c r="B262" t="s">
+        <v>288</v>
+      </c>
+      <c r="C262" t="s">
+        <v>4</v>
+      </c>
+      <c r="D262" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A263">
+        <v>241801265</v>
+      </c>
+      <c r="B263" t="s">
+        <v>289</v>
+      </c>
+      <c r="C263" t="s">
+        <v>4</v>
+      </c>
+      <c r="D263" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A264">
+        <v>241801266</v>
+      </c>
+      <c r="B264" t="s">
+        <v>290</v>
+      </c>
+      <c r="C264" t="s">
+        <v>3</v>
+      </c>
+      <c r="D264" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A265">
+        <v>241801267</v>
+      </c>
+      <c r="B265" t="s">
+        <v>55</v>
+      </c>
+      <c r="C265" t="s">
+        <v>3</v>
+      </c>
+      <c r="D265" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A266">
+        <v>241801268</v>
+      </c>
+      <c r="B266" t="s">
+        <v>56</v>
+      </c>
+      <c r="C266" t="s">
+        <v>6</v>
+      </c>
+      <c r="D266" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A267">
+        <v>241801269</v>
+      </c>
+      <c r="B267" t="s">
+        <v>291</v>
+      </c>
+      <c r="C267" t="s">
+        <v>3</v>
+      </c>
+      <c r="D267" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A268">
+        <v>241801270</v>
+      </c>
+      <c r="B268" t="s">
+        <v>57</v>
+      </c>
+      <c r="C268" t="s">
+        <v>5</v>
+      </c>
+      <c r="D268" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A269">
+        <v>241801271</v>
+      </c>
+      <c r="B269" t="s">
+        <v>292</v>
+      </c>
+      <c r="C269" t="s">
+        <v>6</v>
+      </c>
+      <c r="D269" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A270">
+        <v>241801272</v>
+      </c>
+      <c r="B270" t="s">
+        <v>58</v>
+      </c>
+      <c r="C270" t="s">
+        <v>5</v>
+      </c>
+      <c r="D270" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A271">
+        <v>241801273</v>
+      </c>
+      <c r="B271" t="s">
+        <v>293</v>
+      </c>
+      <c r="C271" t="s">
+        <v>342</v>
+      </c>
+      <c r="D271" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A272">
+        <v>241801274</v>
+      </c>
+      <c r="B272" t="s">
+        <v>59</v>
+      </c>
+      <c r="C272" t="s">
+        <v>341</v>
+      </c>
+      <c r="D272" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A273">
+        <v>241801275</v>
+      </c>
+      <c r="B273" t="s">
+        <v>60</v>
+      </c>
+      <c r="C273" t="s">
+        <v>5</v>
+      </c>
+      <c r="D273" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A274">
+        <v>241801276</v>
+      </c>
+      <c r="B274" t="s">
+        <v>294</v>
+      </c>
+      <c r="C274" t="s">
+        <v>5</v>
+      </c>
+      <c r="D274" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A275">
+        <v>241801277</v>
+      </c>
+      <c r="B275" t="s">
+        <v>295</v>
+      </c>
+      <c r="C275" t="s">
+        <v>341</v>
+      </c>
+      <c r="D275" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A276">
+        <v>241801278</v>
+      </c>
+      <c r="B276" t="s">
+        <v>296</v>
+      </c>
+      <c r="C276" t="s">
+        <v>3</v>
+      </c>
+      <c r="D276" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A277">
+        <v>241801279</v>
+      </c>
+      <c r="B277" t="s">
+        <v>297</v>
+      </c>
+      <c r="C277" t="s">
+        <v>4</v>
+      </c>
+      <c r="D277" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A278">
+        <v>241801280</v>
+      </c>
+      <c r="B278" t="s">
+        <v>298</v>
+      </c>
+      <c r="C278" t="s">
+        <v>341</v>
+      </c>
+      <c r="D278" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A279">
+        <v>241801281</v>
+      </c>
+      <c r="B279" t="s">
+        <v>299</v>
+      </c>
+      <c r="C279" t="s">
+        <v>6</v>
+      </c>
+      <c r="D279" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A280">
+        <v>241801282</v>
+      </c>
+      <c r="B280" t="s">
+        <v>61</v>
+      </c>
+      <c r="C280" t="s">
+        <v>342</v>
+      </c>
+      <c r="D280" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A281">
+        <v>241801283</v>
+      </c>
+      <c r="B281" t="s">
+        <v>300</v>
+      </c>
+      <c r="C281" t="s">
+        <v>341</v>
+      </c>
+      <c r="D281" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A282">
+        <v>241801284</v>
+      </c>
+      <c r="B282" t="s">
+        <v>62</v>
+      </c>
+      <c r="C282" t="s">
+        <v>3</v>
+      </c>
+      <c r="D282" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A283">
+        <v>241801285</v>
+      </c>
+      <c r="B283" t="s">
+        <v>301</v>
+      </c>
+      <c r="C283" t="s">
+        <v>341</v>
+      </c>
+      <c r="D283" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A284">
+        <v>241801286</v>
+      </c>
+      <c r="B284" t="s">
+        <v>302</v>
+      </c>
+      <c r="C284" t="s">
+        <v>342</v>
+      </c>
+      <c r="D284" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A285">
+        <v>241801287</v>
+      </c>
+      <c r="B285" t="s">
+        <v>303</v>
+      </c>
+      <c r="C285" t="s">
+        <v>341</v>
+      </c>
+      <c r="D285" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A286">
+        <v>241801288</v>
+      </c>
+      <c r="B286" t="s">
+        <v>304</v>
+      </c>
+      <c r="C286" t="s">
+        <v>4</v>
+      </c>
+      <c r="D286" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A287">
+        <v>241801289</v>
+      </c>
+      <c r="B287" t="s">
+        <v>305</v>
+      </c>
+      <c r="C287" t="s">
+        <v>342</v>
+      </c>
+      <c r="D287" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A288">
+        <v>241801290</v>
+      </c>
+      <c r="B288" t="s">
+        <v>306</v>
+      </c>
+      <c r="C288" t="s">
+        <v>6</v>
+      </c>
+      <c r="D288" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A289">
+        <v>241801291</v>
+      </c>
+      <c r="B289" t="s">
+        <v>63</v>
+      </c>
+      <c r="C289" t="s">
+        <v>3</v>
+      </c>
+      <c r="D289" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A290">
+        <v>241801292</v>
+      </c>
+      <c r="B290" t="s">
+        <v>307</v>
+      </c>
+      <c r="C290" t="s">
+        <v>4</v>
+      </c>
+      <c r="D290" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A291">
+        <v>241801293</v>
+      </c>
+      <c r="B291" t="s">
+        <v>64</v>
+      </c>
+      <c r="C291" t="s">
+        <v>3</v>
+      </c>
+      <c r="D291" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A292">
+        <v>241801294</v>
+      </c>
+      <c r="B292" t="s">
+        <v>65</v>
+      </c>
+      <c r="C292" t="s">
+        <v>5</v>
+      </c>
+      <c r="D292" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A293">
+        <v>241801295</v>
+      </c>
+      <c r="B293" t="s">
+        <v>308</v>
+      </c>
+      <c r="C293" t="s">
+        <v>6</v>
+      </c>
+      <c r="D293" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A294">
+        <v>241801296</v>
+      </c>
+      <c r="B294" t="s">
+        <v>309</v>
+      </c>
+      <c r="C294" t="s">
+        <v>5</v>
+      </c>
+      <c r="D294" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A295">
+        <v>241801297</v>
+      </c>
+      <c r="B295" t="s">
+        <v>66</v>
+      </c>
+      <c r="C295" t="s">
+        <v>341</v>
+      </c>
+      <c r="D295" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A296">
+        <v>241801298</v>
+      </c>
+      <c r="B296" t="s">
+        <v>67</v>
+      </c>
+      <c r="C296" t="s">
+        <v>5</v>
+      </c>
+      <c r="D296" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A297">
+        <v>241801299</v>
+      </c>
+      <c r="B297" t="s">
+        <v>310</v>
+      </c>
+      <c r="C297" t="s">
+        <v>341</v>
+      </c>
+      <c r="D297" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A298">
+        <v>241801300</v>
+      </c>
+      <c r="B298" t="s">
+        <v>68</v>
+      </c>
+      <c r="C298" t="s">
+        <v>4</v>
+      </c>
+      <c r="D298" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A299">
+        <v>241801301</v>
+      </c>
+      <c r="B299" t="s">
+        <v>311</v>
+      </c>
+      <c r="C299" t="s">
+        <v>6</v>
+      </c>
+      <c r="D299" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A300">
+        <v>241801302</v>
+      </c>
+      <c r="B300" t="s">
+        <v>312</v>
+      </c>
+      <c r="C300" t="s">
+        <v>5</v>
+      </c>
+      <c r="D300" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A301">
+        <v>241801303</v>
+      </c>
+      <c r="B301" t="s">
+        <v>313</v>
+      </c>
+      <c r="C301" t="s">
+        <v>342</v>
+      </c>
+      <c r="D301" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A302">
+        <v>241801304</v>
+      </c>
+      <c r="B302" t="s">
+        <v>314</v>
+      </c>
+      <c r="C302" t="s">
+        <v>3</v>
+      </c>
+      <c r="D302" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A303">
+        <v>241801305</v>
+      </c>
+      <c r="B303" t="s">
+        <v>315</v>
+      </c>
+      <c r="C303" t="s">
+        <v>5</v>
+      </c>
+      <c r="D303" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A304">
+        <v>241801306</v>
+      </c>
+      <c r="B304" t="s">
+        <v>316</v>
+      </c>
+      <c r="C304" t="s">
+        <v>3</v>
+      </c>
+      <c r="D304" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A305">
+        <v>241801307</v>
+      </c>
+      <c r="B305" t="s">
+        <v>317</v>
+      </c>
+      <c r="C305" t="s">
+        <v>4</v>
+      </c>
+      <c r="D305" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A306">
+        <v>241801308</v>
+      </c>
+      <c r="B306" t="s">
+        <v>318</v>
+      </c>
+      <c r="C306" t="s">
+        <v>341</v>
+      </c>
+      <c r="D306" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A307">
+        <v>241801309</v>
+      </c>
+      <c r="B307" t="s">
+        <v>319</v>
+      </c>
+      <c r="C307" t="s">
+        <v>341</v>
+      </c>
+      <c r="D307" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A308">
+        <v>241801310</v>
+      </c>
+      <c r="B308" t="s">
+        <v>69</v>
+      </c>
+      <c r="C308" t="s">
+        <v>342</v>
+      </c>
+      <c r="D308" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A309">
+        <v>241801311</v>
+      </c>
+      <c r="B309" t="s">
+        <v>70</v>
+      </c>
+      <c r="C309" t="s">
+        <v>4</v>
+      </c>
+      <c r="D309" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A310">
+        <v>241801312</v>
+      </c>
+      <c r="B310" t="s">
+        <v>320</v>
+      </c>
+      <c r="C310" t="s">
+        <v>342</v>
+      </c>
+      <c r="D310" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A311">
+        <v>241801313</v>
+      </c>
+      <c r="B311" t="s">
+        <v>321</v>
+      </c>
+      <c r="C311" t="s">
+        <v>5</v>
+      </c>
+      <c r="D311" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A312">
+        <v>241801314</v>
+      </c>
+      <c r="B312" t="s">
+        <v>322</v>
+      </c>
+      <c r="C312" t="s">
+        <v>6</v>
+      </c>
+      <c r="D312" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A313">
+        <v>241801315</v>
+      </c>
+      <c r="B313" t="s">
+        <v>71</v>
+      </c>
+      <c r="C313" t="s">
+        <v>3</v>
+      </c>
+      <c r="D313" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A314">
+        <v>241801316</v>
+      </c>
+      <c r="B314" t="s">
+        <v>323</v>
+      </c>
+      <c r="C314" t="s">
+        <v>4</v>
+      </c>
+      <c r="D314" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A315">
+        <v>241801317</v>
+      </c>
+      <c r="B315" t="s">
+        <v>72</v>
+      </c>
+      <c r="C315" t="s">
+        <v>341</v>
+      </c>
+      <c r="D315" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A316">
+        <v>241801318</v>
+      </c>
+      <c r="B316" t="s">
+        <v>324</v>
+      </c>
+      <c r="C316" t="s">
+        <v>4</v>
+      </c>
+      <c r="D316" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A317">
+        <v>241801319</v>
+      </c>
+      <c r="B317" t="s">
+        <v>325</v>
+      </c>
+      <c r="C317" t="s">
+        <v>342</v>
+      </c>
+      <c r="D317" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A318">
+        <v>241801320</v>
+      </c>
+      <c r="B318" t="s">
+        <v>326</v>
+      </c>
+      <c r="C318" t="s">
+        <v>342</v>
+      </c>
+      <c r="D318" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A319">
+        <v>241801321</v>
+      </c>
+      <c r="B319" t="s">
+        <v>327</v>
+      </c>
+      <c r="C319" t="s">
+        <v>341</v>
+      </c>
+      <c r="D319" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A320">
+        <v>241801322</v>
+      </c>
+      <c r="B320" t="s">
+        <v>328</v>
+      </c>
+      <c r="C320" t="s">
+        <v>3</v>
+      </c>
+      <c r="D320" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A321">
+        <v>241801323</v>
+      </c>
+      <c r="B321" t="s">
+        <v>73</v>
+      </c>
+      <c r="C321" t="s">
+        <v>3</v>
+      </c>
+      <c r="D321" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A322">
+        <v>241801324</v>
+      </c>
+      <c r="B322" t="s">
+        <v>329</v>
+      </c>
+      <c r="C322" t="s">
+        <v>5</v>
+      </c>
+      <c r="D322" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A323">
         <v>241801325</v>
       </c>
-      <c r="B71" t="s">
-        <v>76</v>
-      </c>
-      <c r="C71" t="s">
-        <v>79</v>
-      </c>
-      <c r="D71" t="s">
-        <v>4</v>
+      <c r="B323" t="s">
+        <v>74</v>
+      </c>
+      <c r="C323" t="s">
+        <v>341</v>
+      </c>
+      <c r="D323" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A324">
+        <v>241801326</v>
+      </c>
+      <c r="B324" t="s">
+        <v>330</v>
+      </c>
+      <c r="C324" t="s">
+        <v>341</v>
+      </c>
+      <c r="D324" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A325">
+        <v>241801327</v>
+      </c>
+      <c r="B325" t="s">
+        <v>331</v>
+      </c>
+      <c r="C325" t="s">
+        <v>5</v>
+      </c>
+      <c r="D325" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A326">
+        <v>241801328</v>
+      </c>
+      <c r="B326" t="s">
+        <v>332</v>
+      </c>
+      <c r="C326" t="s">
+        <v>4</v>
+      </c>
+      <c r="D326" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A327">
+        <v>241801329</v>
+      </c>
+      <c r="B327" t="s">
+        <v>333</v>
+      </c>
+      <c r="C327" t="s">
+        <v>341</v>
+      </c>
+      <c r="D327" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A328">
+        <v>241801504</v>
+      </c>
+      <c r="B328" t="s">
+        <v>334</v>
+      </c>
+      <c r="C328" t="s">
+        <v>4</v>
+      </c>
+      <c r="D328" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A329">
+        <v>241801505</v>
+      </c>
+      <c r="B329" t="s">
+        <v>335</v>
+      </c>
+      <c r="C329" t="s">
+        <v>341</v>
+      </c>
+      <c r="D329" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A330">
+        <v>241801506</v>
+      </c>
+      <c r="B330" t="s">
+        <v>336</v>
+      </c>
+      <c r="C330" t="s">
+        <v>4</v>
+      </c>
+      <c r="D330" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A331">
+        <v>241801507</v>
+      </c>
+      <c r="B331" t="s">
+        <v>337</v>
+      </c>
+      <c r="C331" t="s">
+        <v>6</v>
+      </c>
+      <c r="D331" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A332">
+        <v>241801508</v>
+      </c>
+      <c r="B332" t="s">
+        <v>338</v>
+      </c>
+      <c r="C332" t="s">
+        <v>4</v>
+      </c>
+      <c r="D332" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A333">
+        <v>241801510</v>
+      </c>
+      <c r="B333" t="s">
+        <v>339</v>
+      </c>
+      <c r="C333" t="s">
+        <v>4</v>
+      </c>
+      <c r="D333" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A334">
+        <v>241801511</v>
+      </c>
+      <c r="B334" t="s">
+        <v>340</v>
+      </c>
+      <c r="C334" t="s">
+        <v>3</v>
+      </c>
+      <c r="D334" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
